--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20232.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -85,73 +85,49 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>MOLOHUA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SORIA</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERNANDO</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
   </si>
   <si>
     <t>YAHIR</t>
   </si>
   <si>
+    <t>MIGUEL</t>
+  </si>
+  <si>
     <t>JESUS EMMANUEL</t>
   </si>
   <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>MARIO</t>
-  </si>
-  <si>
-    <t>JHOSUA LEVY</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
+    <t>ALBERTO SHAKIB</t>
   </si>
 </sst>
 </file>
@@ -747,16 +723,19 @@
         <v>29</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>93.09999999999999</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -770,16 +749,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>93.55</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -793,16 +775,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>76.67</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -816,16 +801,19 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>95.83</v>
+      </c>
+      <c r="H5">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -839,16 +827,19 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>73.08</v>
+      </c>
+      <c r="H6">
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -862,16 +853,19 @@
         <v>14</v>
       </c>
       <c r="D7">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>64.29000000000001</v>
+      </c>
+      <c r="H7">
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -927,13 +921,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>96.55</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H2">
         <v>8.6</v>
@@ -962,7 +956,7 @@
         <v>93.55</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -979,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>70</v>
+        <v>76.67</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1014,7 +1008,7 @@
         <v>95.83</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1031,16 +1025,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6">
-        <v>76.92</v>
+        <v>73.08</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1057,13 +1051,13 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>71.43000000000001</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="H7">
         <v>7.6</v>
@@ -1076,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1108,22 +1102,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920189</v>
+        <v>21330051920153</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1131,16 +1125,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920162</v>
+        <v>21330051920171</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1154,22 +1148,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920171</v>
+        <v>21330051920379</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1183,10 +1177,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1200,93 +1194,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920153</v>
+        <v>21330051920141</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920159</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920175</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920010</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20232.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="40">
   <si>
     <t>Mat</t>
   </si>
@@ -85,49 +85,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>AGUILAR</t>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
   </si>
   <si>
     <t>MOLOHUA</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SORIA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
+    <t>OSMAR UZIEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>ROBERTO</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>YAHIR</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
-  </si>
-  <si>
-    <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>ALBERTO SHAKIB</t>
   </si>
 </sst>
 </file>
@@ -655,7 +664,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -664,13 +673,13 @@
         <v>4</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -850,7 +859,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -859,13 +868,13 @@
         <v>5</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -973,16 +982,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>76.67</v>
+        <v>90</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1025,16 +1034,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>73.08</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1045,22 +1054,22 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7">
-        <v>64.29000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1070,7 +1079,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1102,22 +1111,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920153</v>
+        <v>22330051920382</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1125,22 +1134,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920171</v>
+        <v>22330051920189</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1148,22 +1157,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920379</v>
+        <v>21330051920165</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1171,22 +1180,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920021</v>
+        <v>21330051920135</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1194,16 +1203,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920141</v>
+        <v>21330051920382</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1212,6 +1221,29 @@
         <v>15</v>
       </c>
       <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920171</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20232.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -85,12 +85,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
     <t>LORENZO</t>
   </si>
   <si>
@@ -103,12 +97,6 @@
     <t>MOLOHUA</t>
   </si>
   <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>ROSETE</t>
   </si>
   <si>
@@ -119,12 +107,6 @@
   </si>
   <si>
     <t>MIXCOHUA</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
   </si>
   <si>
     <t>ROBERTO</t>
@@ -930,16 +912,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>93.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -956,16 +938,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>93.55</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1079,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1111,22 +1093,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920382</v>
+        <v>21330051920165</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1134,22 +1116,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920189</v>
+        <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1157,22 +1139,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920165</v>
+        <v>21330051920382</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1180,70 +1162,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920135</v>
+        <v>21330051920171</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920382</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920171</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
         <v>1</v>
       </c>
     </row>
